--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N57_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N57_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>8.677003309995229</v>
+        <v>1.410013037874225</v>
       </c>
       <c r="D2" t="n">
-        <v>10.92323088927764</v>
+        <v>1.775025019507616</v>
       </c>
       <c r="E2" t="n">
-        <v>15.46660848095171</v>
+        <v>2.513323878154652</v>
       </c>
       <c r="F2" t="n">
-        <v>15.72196319468357</v>
+        <v>2.554819019136079</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.12576017045958</v>
+        <v>8.470436027699682</v>
       </c>
       <c r="D3" t="n">
-        <v>51.69426114071096</v>
+        <v>8.400317435365531</v>
       </c>
       <c r="E3" t="n">
-        <v>15.46660848095171</v>
+        <v>2.513323878154652</v>
       </c>
       <c r="F3" t="n">
-        <v>15.72196319468357</v>
+        <v>2.554819019136079</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>47.8305494081966</v>
+        <v>7.772464278831948</v>
       </c>
       <c r="D4" t="n">
-        <v>47.78687514800022</v>
+        <v>7.765367211550036</v>
       </c>
       <c r="E4" t="n">
-        <v>15.46660848095171</v>
+        <v>2.513323878154652</v>
       </c>
       <c r="F4" t="n">
-        <v>15.72196319468357</v>
+        <v>2.554819019136079</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.15013296002918</v>
+        <v>7.499396606004742</v>
       </c>
       <c r="D5" t="n">
-        <v>45.16946339579134</v>
+        <v>7.340037801816093</v>
       </c>
       <c r="E5" t="n">
-        <v>15.46660848095171</v>
+        <v>2.513323878154652</v>
       </c>
       <c r="F5" t="n">
-        <v>15.72196319468357</v>
+        <v>2.554819019136079</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>52.21861278462075</v>
+        <v>8.485524577500872</v>
       </c>
       <c r="D6" t="n">
-        <v>51.25578188704598</v>
+        <v>8.329064556644973</v>
       </c>
       <c r="E6" t="n">
-        <v>15.46660848095171</v>
+        <v>2.513323878154652</v>
       </c>
       <c r="F6" t="n">
-        <v>15.72196319468357</v>
+        <v>2.554819019136079</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.92031047026398</v>
+        <v>6.974550451417898</v>
       </c>
       <c r="D7" t="n">
-        <v>43.09779603070056</v>
+        <v>7.003391854988841</v>
       </c>
       <c r="E7" t="n">
-        <v>15.46660848095171</v>
+        <v>2.513323878154652</v>
       </c>
       <c r="F7" t="n">
-        <v>15.72196319468357</v>
+        <v>2.554819019136079</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>40.36558733215342</v>
+        <v>6.55940794147493</v>
       </c>
       <c r="D8" t="n">
-        <v>39.3338171408156</v>
+        <v>6.391745285382536</v>
       </c>
       <c r="E8" t="n">
-        <v>15.46660848095171</v>
+        <v>2.513323878154652</v>
       </c>
       <c r="F8" t="n">
-        <v>15.72196319468357</v>
+        <v>2.554819019136079</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>54.0899996220076</v>
+        <v>8.789624938576235</v>
       </c>
       <c r="D9" t="n">
-        <v>41.24478631945674</v>
+        <v>6.702277776911721</v>
       </c>
       <c r="E9" t="n">
-        <v>15.46660848095171</v>
+        <v>2.513323878154652</v>
       </c>
       <c r="F9" t="n">
-        <v>15.72196319468357</v>
+        <v>2.554819019136079</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>46.26097104210088</v>
+        <v>7.517407794341393</v>
       </c>
       <c r="D10" t="n">
-        <v>46.80115549512166</v>
+        <v>7.60518776795727</v>
       </c>
       <c r="E10" t="n">
-        <v>15.46660848095171</v>
+        <v>2.513323878154652</v>
       </c>
       <c r="F10" t="n">
-        <v>15.72196319468357</v>
+        <v>2.554819019136079</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>55.7064788771368</v>
+        <v>9.052302817534731</v>
       </c>
       <c r="D11" t="n">
-        <v>34.14191965572202</v>
+        <v>5.548061944054829</v>
       </c>
       <c r="E11" t="n">
-        <v>15.46660848095171</v>
+        <v>2.513323878154652</v>
       </c>
       <c r="F11" t="n">
-        <v>15.72196319468357</v>
+        <v>2.554819019136079</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>24.36772566858467</v>
+        <v>3.959755421145008</v>
       </c>
       <c r="D12" t="n">
-        <v>25.20627327048721</v>
+        <v>4.096019406454172</v>
       </c>
       <c r="E12" t="n">
-        <v>15.46660848095171</v>
+        <v>2.513323878154652</v>
       </c>
       <c r="F12" t="n">
-        <v>15.72196319468357</v>
+        <v>2.554819019136079</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>34.23807605155151</v>
+        <v>5.563687358377121</v>
       </c>
       <c r="D13" t="n">
-        <v>13.24452148234757</v>
+        <v>2.15223474088148</v>
       </c>
       <c r="E13" t="n">
-        <v>15.46660848095171</v>
+        <v>2.513323878154652</v>
       </c>
       <c r="F13" t="n">
-        <v>15.72196319468357</v>
+        <v>2.554819019136079</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>15.11108286635614</v>
+        <v>2.455550965782873</v>
       </c>
       <c r="D14" t="n">
-        <v>15.29166014870913</v>
+        <v>2.484894774165234</v>
       </c>
       <c r="E14" t="n">
-        <v>15.46660848095171</v>
+        <v>2.513323878154652</v>
       </c>
       <c r="F14" t="n">
-        <v>15.72196319468357</v>
+        <v>2.554819019136079</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>17.57415946954028</v>
+        <v>2.855800913800296</v>
       </c>
       <c r="D15" t="n">
-        <v>18.46374605974517</v>
+        <v>3.000358734708589</v>
       </c>
       <c r="E15" t="n">
-        <v>15.46660848095171</v>
+        <v>2.513323878154652</v>
       </c>
       <c r="F15" t="n">
-        <v>15.72196319468357</v>
+        <v>2.554819019136079</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>53.090867722036</v>
+        <v>8.627266004830851</v>
       </c>
       <c r="D16" t="n">
-        <v>54.00834682875825</v>
+        <v>8.776356359673215</v>
       </c>
       <c r="E16" t="n">
-        <v>15.46660848095171</v>
+        <v>2.513323878154652</v>
       </c>
       <c r="F16" t="n">
-        <v>15.72196319468357</v>
+        <v>2.554819019136079</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>15.34671316400589</v>
+        <v>2.493840889150957</v>
       </c>
       <c r="D17" t="n">
-        <v>6.245245104858022</v>
+        <v>1.014852329539428</v>
       </c>
       <c r="E17" t="n">
-        <v>15.46660848095171</v>
+        <v>2.513323878154652</v>
       </c>
       <c r="F17" t="n">
-        <v>15.72196319468357</v>
+        <v>2.554819019136079</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>25.61817693675117</v>
+        <v>4.162953752222066</v>
       </c>
       <c r="D18" t="n">
-        <v>26.83515009740824</v>
+        <v>4.360711890828838</v>
       </c>
       <c r="E18" t="n">
-        <v>15.46660848095171</v>
+        <v>2.513323878154652</v>
       </c>
       <c r="F18" t="n">
-        <v>15.72196319468357</v>
+        <v>2.554819019136079</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>44.93259096390057</v>
+        <v>7.301546031633842</v>
       </c>
       <c r="D19" t="n">
-        <v>45.90809237666136</v>
+        <v>7.460065011207471</v>
       </c>
       <c r="E19" t="n">
-        <v>15.46660848095171</v>
+        <v>2.513323878154652</v>
       </c>
       <c r="F19" t="n">
-        <v>15.72196319468357</v>
+        <v>2.554819019136079</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>17.83644832607907</v>
+        <v>2.898422852987849</v>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>2.03125</v>
       </c>
       <c r="E20" t="n">
-        <v>15.46660848095171</v>
+        <v>2.513323878154652</v>
       </c>
       <c r="F20" t="n">
-        <v>15.72196319468357</v>
+        <v>2.554819019136079</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
